--- a/public/templates/examples/A-087-TrainingCompletionRecords-EXAMPLE-M.xlsx
+++ b/public/templates/examples/A-087-TrainingCompletionRecords-EXAMPLE-M.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -205,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -264,6 +269,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,7 +663,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="8" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -715,7 +727,7 @@
       <c r="E6" s="21" t="n"/>
       <c r="F6" s="20" t="n"/>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="98.0" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Coverage / Scope</t>
@@ -742,7 +754,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="8" t="n"/>
     </row>
-    <row r="11" ht="27.75" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
           <t>Staff Member (Name &amp; Role)</t>
@@ -790,23 +802,19 @@
           <t>General</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D12" s="26">
+        <v>46042</v>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
+      <c r="F12" s="26">
+        <v>46407</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Dana Mercer, Security Coordinator</t>
@@ -822,20 +830,16 @@
           <t>Role-based</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
+      <c r="D13" s="26">
+        <v>46058</v>
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Pass 98%</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>2027-02-05</t>
-        </is>
+      <c r="F13" s="26">
+        <v>46423</v>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1">
@@ -854,20 +858,16 @@
           <t>Role-based</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>2026-02-05</t>
-        </is>
+      <c r="D14" s="26">
+        <v>46058</v>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
           <t>Pass 90%</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>2027-02-05</t>
-        </is>
+      <c r="F14" s="26">
+        <v>46423</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
@@ -886,20 +886,16 @@
           <t>General</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D15" s="26">
+        <v>46042</v>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
+      <c r="F15" s="26">
+        <v>46407</v>
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1">
@@ -918,20 +914,16 @@
           <t>General</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="D16" s="26">
+        <v>46042</v>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>2027-01-20</t>
-        </is>
+      <c r="F16" s="26">
+        <v>46407</v>
       </c>
     </row>
     <row r="17" ht="19.5" customHeight="1">
@@ -950,20 +942,16 @@
           <t>General</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+      <c r="D17" s="26">
+        <v>46188</v>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>2027-06-15</t>
-        </is>
+      <c r="F17" s="26">
+        <v>46553</v>
       </c>
     </row>
     <row r="18" ht="19.5" customHeight="1">
@@ -1009,7 +997,7 @@
     <row r="24" ht="29.75" customHeight="1">
       <c r="A24" s="8" t="n"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25" ht="34.7" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Completion for the period: 14 of 14 required staff current (100%) against the 100% target. One role-based refresh (county IT) is due next quarter and scheduled.</t>
@@ -1064,10 +1052,8 @@
           <t>/s/ Dana Mercer</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
+      <c r="D29" s="25">
+        <v>46073</v>
       </c>
       <c r="E29" s="13" t="n"/>
       <c r="F29" s="13" t="n"/>
@@ -1088,10 +1074,8 @@
           <t>/s/ Anthony Reyes</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
+      <c r="D30" s="25">
+        <v>46073</v>
       </c>
       <c r="E30" s="13" t="n"/>
       <c r="F30" s="13" t="n"/>
@@ -1162,7 +1146,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="34.7" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1192,10 +1176,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
+      <c r="B46" s="24">
+        <v>46073</v>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
@@ -1211,11 +1193,11 @@
       <c r="F46" s="11" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -1238,7 +1220,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A4:B4"/>
@@ -1247,7 +1228,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>